--- a/data/models/sk-hynix.xlsx
+++ b/data/models/sk-hynix.xlsx
@@ -826,7 +826,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="14" t="n">
-        <v>131.62</v>
+        <v>131.69</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -835,7 +835,7 @@
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">C10/C11-1</f>
-        <v>-0.0574989830803495</v>
+        <v>-0.0579999707877257</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
